--- a/DateBase/orders/Nha Thu_2026-7-27.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-27.xlsx
@@ -947,6 +947,9 @@
       <c r="C60" t="str">
         <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
+      <c r="F60" t="str">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -1005,7 +1008,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>020101510555510105101055105121515201010101010105510151010978101041510102010201010101010155201515101050</v>
+        <v>020101510555510105101055105121515201010101010105510151010978101041510102010201010101010155201515101051</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-7-27.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-27.xlsx
@@ -948,7 +948,7 @@
         <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
       <c r="F60" t="str">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1008,7 +1008,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>020101510555510105101055105121515201010101010105510151010978101041510102010201010101010155201515101051</v>
+        <v>0201015105555101051010551051215152010101010101055101510109781010415101020102010101010101552015151010515</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-7-27.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-27.xlsx
@@ -1010,6 +1010,9 @@
       <c r="G2" t="str">
         <v>0201015105555101051010551051215152010101010101055101510109781010415101020102010101010101552015151010515</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
